--- a/Data/TestData.xlsx
+++ b/Data/TestData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>Fruits</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>RandomPassword: lhWAs14ERandomEmail: XHKQrv@gmailAccountCreated</t>
+  </si>
+  <si>
+    <t>RandomPassword: oLY0FqRrRandomEmail: jIUrdI@gmailAccountCreated</t>
   </si>
 </sst>
 </file>
@@ -580,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="50.7109375"/>
@@ -987,6 +990,11 @@
         <v>77</v>
       </c>
     </row>
+    <row r="78">
+      <c r="C78" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/TestData.xlsx
+++ b/Data/TestData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>Fruits</t>
   </si>
@@ -251,13 +251,42 @@
   </si>
   <si>
     <t>RandomPassword: oLY0FqRrRandomEmail: jIUrdI@gmailAccountCreated</t>
+  </si>
+  <si>
+    <t>bye</t>
+  </si>
+  <si>
+    <t>RandomPassword: 6uqpl1mnRandomEmail: DOBzRd@gmailAccountCreated</t>
+  </si>
+  <si>
+    <t>RandomPassword: 6uqpl1mnRandomEmail: DOBzRd@gmailAccountDeleted</t>
+  </si>
+  <si>
+    <t>RandomPassword: HtJpg2RmRandomEmail: HvAKBZ@gmailAccountCreated</t>
+  </si>
+  <si>
+    <t>RandomPassword: IQvw7r9iRandomEmail: qGcPLf@gmailAccountCreated</t>
+  </si>
+  <si>
+    <t>RandomPassword: yI9H9yBORandomEmail: OEuEdV@gmailAccountCreated</t>
+  </si>
+  <si>
+    <t>RandomPassword: yI9H9yBORandomEmail: OEuEdV@gmailAccountDeleted</t>
+  </si>
+  <si>
+    <t>RandomPassword: FFZw6g5mRandomEmail: pjjfAv@gmailAccountCreated</t>
+  </si>
+  <si>
+    <t>RandomPassword: utcmaLXQRandomEmail: aMAFHM@gmailAccountCreated</t>
+  </si>
+  <si>
+    <t>RandomPassword: tYAgZON5RandomEmail: mZXZpD@gmailAccountCreated</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -583,416 +612,466 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="50.7109375"/>
-    <col min="2" max="2" customWidth="true" width="56.140625"/>
+    <col min="1" max="1" width="50.7109375" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s" s="0">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B2">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s" s="0">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="0">
+      <c r="B3">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s" s="0">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="0">
+      <c r="B4">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s" s="0">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="0">
+      <c r="B5">
         <v>120</v>
       </c>
     </row>
-    <row r="6">
-      <c r="C6" t="s" s="0">
+    <row r="6" spans="1:3">
+      <c r="C6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7">
-      <c r="C7" t="s" s="0">
+    <row r="7" spans="1:3">
+      <c r="C7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8">
-      <c r="C8" t="s" s="0">
+    <row r="8" spans="1:3">
+      <c r="C8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9">
-      <c r="C9" t="s" s="0">
+    <row r="9" spans="1:3">
+      <c r="C9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10">
-      <c r="C10" t="s" s="0">
+    <row r="10" spans="1:3">
+      <c r="C10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11">
-      <c r="C11" t="s" s="0">
+    <row r="11" spans="1:3">
+      <c r="C11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12">
-      <c r="C12" t="s" s="0">
+    <row r="12" spans="1:3">
+      <c r="C12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" t="s" s="0">
+    <row r="13" spans="1:3">
+      <c r="C13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14">
-      <c r="C14" t="s" s="0">
+    <row r="14" spans="1:3">
+      <c r="C14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15">
-      <c r="C15" t="s" s="0">
+    <row r="15" spans="1:3">
+      <c r="C15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16">
-      <c r="C16" t="s" s="0">
+    <row r="16" spans="1:3">
+      <c r="C16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17">
-      <c r="C17" t="s" s="0">
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18">
-      <c r="C18" t="s" s="0">
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19">
-      <c r="C19" t="s" s="0">
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20">
-      <c r="C20" t="s" s="0">
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21">
-      <c r="C21" t="s" s="0">
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22">
-      <c r="C22" t="s" s="0">
+    <row r="22" spans="3:3">
+      <c r="C22" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23">
-      <c r="C23" t="s" s="0">
+    <row r="23" spans="3:3">
+      <c r="C23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24">
-      <c r="C24" t="s" s="0">
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25">
-      <c r="C25" t="s" s="0">
+    <row r="25" spans="3:3">
+      <c r="C25" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26">
-      <c r="C26" t="s" s="0">
+    <row r="26" spans="3:3">
+      <c r="C26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27">
-      <c r="C27" t="s" s="0">
+    <row r="27" spans="3:3">
+      <c r="C27" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28">
-      <c r="C28" t="s" s="0">
+    <row r="28" spans="3:3">
+      <c r="C28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29">
-      <c r="C29" t="s" s="0">
+    <row r="29" spans="3:3">
+      <c r="C29" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30">
-      <c r="C30" t="s" s="0">
+    <row r="30" spans="3:3">
+      <c r="C30" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31">
-      <c r="C31" t="s" s="0">
+    <row r="31" spans="3:3">
+      <c r="C31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32">
-      <c r="C32" t="s" s="0">
+    <row r="32" spans="3:3">
+      <c r="C32" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33">
-      <c r="C33" t="s" s="0">
+    <row r="33" spans="3:3">
+      <c r="C33" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34">
-      <c r="C34" t="s" s="0">
+    <row r="34" spans="3:3">
+      <c r="C34" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35">
-      <c r="C35" t="s" s="0">
+    <row r="35" spans="3:3">
+      <c r="C35" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36">
-      <c r="C36" t="s" s="0">
+    <row r="36" spans="3:3">
+      <c r="C36" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37">
-      <c r="C37" t="s" s="0">
+    <row r="37" spans="3:3">
+      <c r="C37" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38">
-      <c r="C38" t="s" s="0">
+    <row r="38" spans="3:3">
+      <c r="C38" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="39">
-      <c r="C39" t="s" s="0">
+    <row r="39" spans="3:3">
+      <c r="C39" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="40">
-      <c r="C40" t="s" s="0">
+    <row r="40" spans="3:3">
+      <c r="C40" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="41">
-      <c r="C41" t="s" s="0">
+    <row r="41" spans="3:3">
+      <c r="C41" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="42">
-      <c r="C42" t="s" s="0">
+    <row r="42" spans="3:3">
+      <c r="C42" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43">
-      <c r="C43" t="s" s="0">
+    <row r="43" spans="3:3">
+      <c r="C43" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="44">
-      <c r="C44" t="s" s="0">
+    <row r="44" spans="3:3">
+      <c r="C44" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="45">
-      <c r="C45" t="s" s="0">
+    <row r="45" spans="3:3">
+      <c r="C45" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="46">
-      <c r="C46" t="s" s="0">
+    <row r="46" spans="3:3">
+      <c r="C46" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="47">
-      <c r="C47" t="s" s="0">
+    <row r="47" spans="3:3">
+      <c r="C47" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="48">
-      <c r="C48" t="s" s="0">
+    <row r="48" spans="3:3">
+      <c r="C48" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="49">
-      <c r="C49" t="s" s="0">
+    <row r="49" spans="3:3">
+      <c r="C49" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="50">
-      <c r="C50" t="s" s="0">
+    <row r="50" spans="3:3">
+      <c r="C50" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="51">
-      <c r="C51" t="s" s="0">
+    <row r="51" spans="3:3">
+      <c r="C51" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="52">
-      <c r="C52" t="s" s="0">
+    <row r="52" spans="3:3">
+      <c r="C52" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="53">
-      <c r="C53" t="s" s="0">
+    <row r="53" spans="3:3">
+      <c r="C53" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="54">
-      <c r="C54" t="s" s="0">
+    <row r="54" spans="3:3">
+      <c r="C54" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="55">
-      <c r="C55" t="s" s="0">
+    <row r="55" spans="3:3">
+      <c r="C55" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="56">
-      <c r="C56" t="s" s="0">
+    <row r="56" spans="3:3">
+      <c r="C56" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="57">
-      <c r="C57" t="s" s="0">
+    <row r="57" spans="3:3">
+      <c r="C57" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="58">
-      <c r="C58" t="s" s="0">
+    <row r="58" spans="3:3">
+      <c r="C58" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="59">
-      <c r="C59" t="s" s="0">
+    <row r="59" spans="3:3">
+      <c r="C59" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="60">
-      <c r="C60" t="s" s="0">
+    <row r="60" spans="3:3">
+      <c r="C60" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="61">
-      <c r="C61" t="s" s="0">
+    <row r="61" spans="3:3">
+      <c r="C61" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="62">
-      <c r="C62" t="s" s="0">
+    <row r="62" spans="3:3">
+      <c r="C62" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="63">
-      <c r="C63" t="s" s="0">
+    <row r="63" spans="3:3">
+      <c r="C63" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="64">
-      <c r="C64" t="s" s="0">
+    <row r="64" spans="3:3">
+      <c r="C64" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="65">
-      <c r="C65" t="s" s="0">
+    <row r="65" spans="3:3">
+      <c r="C65" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="66">
-      <c r="C66" t="s" s="0">
+    <row r="66" spans="3:3">
+      <c r="C66" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="67">
-      <c r="C67" t="s" s="0">
+    <row r="67" spans="3:3">
+      <c r="C67" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="68">
-      <c r="C68" t="s" s="0">
+    <row r="68" spans="3:3">
+      <c r="C68" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="69">
-      <c r="C69" t="s" s="0">
+    <row r="69" spans="3:3">
+      <c r="C69" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="70">
-      <c r="C70" t="s" s="0">
+    <row r="70" spans="3:3">
+      <c r="C70" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="71">
-      <c r="C71" t="s" s="0">
+    <row r="71" spans="3:3">
+      <c r="C71" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72">
-      <c r="C72" t="s" s="0">
+    <row r="72" spans="3:3">
+      <c r="C72" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="73">
-      <c r="C73" t="s" s="0">
+    <row r="73" spans="3:3">
+      <c r="C73" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="74">
-      <c r="C74" t="s" s="0">
+    <row r="74" spans="3:3">
+      <c r="C74" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="75">
-      <c r="C75" t="s" s="0">
+    <row r="75" spans="3:3">
+      <c r="C75" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="76">
-      <c r="C76" t="s" s="0">
+    <row r="76" spans="3:3">
+      <c r="C76" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="77">
-      <c r="C77" t="s" s="0">
+    <row r="77" spans="3:3">
+      <c r="C77" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="78">
-      <c r="C78" t="s" s="0">
+    <row r="78" spans="3:3">
+      <c r="C78" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="3:3">
+      <c r="C79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="3:3">
+      <c r="C80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3">
+      <c r="C81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3">
+      <c r="C82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3">
+      <c r="C83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3">
+      <c r="C84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3">
+      <c r="C85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3">
+      <c r="C86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
